--- a/backend/data/financials_by_company/1566.HK.xlsx
+++ b/backend/data/financials_by_company/1566.HK.xlsx
@@ -672,152 +672,152 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45382</v>
+        <v>44651</v>
       </c>
       <c r="B2" t="n">
-        <v>-2388355.950041</v>
+        <v>-12714172.147394</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.017309</v>
       </c>
       <c r="D2" t="n">
-        <v>1786000</v>
+        <v>-91722000</v>
       </c>
       <c r="E2" t="n">
-        <v>-27934000</v>
+        <v>-734538000</v>
       </c>
       <c r="F2" t="n">
-        <v>-27934000</v>
+        <v>-734538000</v>
       </c>
       <c r="G2" t="n">
-        <v>-170679000</v>
+        <v>-1050184000</v>
       </c>
       <c r="H2" t="n">
-        <v>66092000</v>
+        <v>172247000</v>
       </c>
       <c r="I2" t="n">
-        <v>308652000</v>
+        <v>390410000</v>
       </c>
       <c r="J2" t="n">
-        <v>-26148000</v>
+        <v>-826260000</v>
       </c>
       <c r="K2" t="n">
-        <v>-92240000</v>
+        <v>-998507000</v>
       </c>
       <c r="L2" t="n">
-        <v>-93937000</v>
+        <v>-80631000</v>
       </c>
       <c r="M2" t="n">
-        <v>93994000</v>
+        <v>80638000</v>
       </c>
       <c r="N2" t="n">
-        <v>57000</v>
+        <v>7000</v>
       </c>
       <c r="O2" t="n">
-        <v>-145133355.950041</v>
+        <v>-328360172.147394</v>
       </c>
       <c r="P2" t="n">
-        <v>-170679000</v>
+        <v>-1050184000</v>
       </c>
       <c r="Q2" t="n">
-        <v>430175000</v>
+        <v>587772000</v>
       </c>
       <c r="R2" t="n">
-        <v>1182042000</v>
+        <v>1033664000</v>
       </c>
       <c r="S2" t="n">
-        <v>1182042000</v>
+        <v>1033664000</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.14</v>
+        <v>-1.02</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.14</v>
+        <v>-1.02</v>
       </c>
       <c r="V2" t="n">
-        <v>-170679000</v>
+        <v>-1050184000</v>
       </c>
       <c r="W2" t="n">
-        <v>-170679000</v>
+        <v>-1050184000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-170679000</v>
+        <v>-1050184000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-368000</v>
+        <v>10282000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-170311000</v>
+        <v>-1060466000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-170311000</v>
+        <v>-1060466000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-15923000</v>
+        <v>-18679000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-186234000</v>
+        <v>-1079145000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1412000</v>
+        <v>890000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-23785000</v>
+        <v>-725744000</v>
       </c>
       <c r="AG2" t="n">
-        <v>10239000</v>
+        <v>86000</v>
       </c>
       <c r="AH2" t="n">
-        <v>29000</v>
+        <v>539452000</v>
       </c>
       <c r="AI2" t="n">
-        <v>13517000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+        <v>186206000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
       <c r="AK2" t="n">
-        <v>-93937000</v>
+        <v>-80631000</v>
       </c>
       <c r="AL2" t="n">
-        <v>93994000</v>
+        <v>80638000</v>
       </c>
       <c r="AM2" t="n">
-        <v>57000</v>
+        <v>7000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-66147000</v>
+        <v>-134636000</v>
       </c>
       <c r="AO2" t="n">
-        <v>121523000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>11847000</v>
-      </c>
+        <v>197362000</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>14907000</v>
+        <v>11678000</v>
       </c>
       <c r="AR2" t="n">
-        <v>95081000</v>
+        <v>195021000</v>
       </c>
       <c r="AS2" t="n">
-        <v>22050000</v>
+        <v>14954000</v>
       </c>
       <c r="AT2" t="n">
-        <v>73031000</v>
+        <v>180067000</v>
       </c>
       <c r="AU2" t="n">
-        <v>55376000</v>
+        <v>62726000</v>
       </c>
       <c r="AV2" t="n">
-        <v>308652000</v>
+        <v>390410000</v>
       </c>
       <c r="AW2" t="n">
-        <v>364028000</v>
+        <v>453136000</v>
       </c>
       <c r="AX2" t="n">
-        <v>364028000</v>
+        <v>453136000</v>
       </c>
     </row>
     <row r="3">
@@ -972,152 +972,152 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44651</v>
+        <v>45382</v>
       </c>
       <c r="B4" t="n">
-        <v>-12714172.147394</v>
+        <v>-2388355.950041</v>
       </c>
       <c r="C4" t="n">
-        <v>0.017309</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>-91722000</v>
+        <v>1786000</v>
       </c>
       <c r="E4" t="n">
-        <v>-734538000</v>
+        <v>-27934000</v>
       </c>
       <c r="F4" t="n">
-        <v>-734538000</v>
+        <v>-27934000</v>
       </c>
       <c r="G4" t="n">
-        <v>-1050184000</v>
+        <v>-170679000</v>
       </c>
       <c r="H4" t="n">
-        <v>172247000</v>
+        <v>66092000</v>
       </c>
       <c r="I4" t="n">
-        <v>390410000</v>
+        <v>308652000</v>
       </c>
       <c r="J4" t="n">
-        <v>-826260000</v>
+        <v>-26148000</v>
       </c>
       <c r="K4" t="n">
-        <v>-998507000</v>
+        <v>-92240000</v>
       </c>
       <c r="L4" t="n">
-        <v>-80631000</v>
+        <v>-93937000</v>
       </c>
       <c r="M4" t="n">
-        <v>80638000</v>
+        <v>93994000</v>
       </c>
       <c r="N4" t="n">
-        <v>7000</v>
+        <v>57000</v>
       </c>
       <c r="O4" t="n">
-        <v>-328360172.147394</v>
+        <v>-145133355.950041</v>
       </c>
       <c r="P4" t="n">
-        <v>-1050184000</v>
+        <v>-170679000</v>
       </c>
       <c r="Q4" t="n">
-        <v>587772000</v>
+        <v>430175000</v>
       </c>
       <c r="R4" t="n">
-        <v>1033664000</v>
+        <v>1182042000</v>
       </c>
       <c r="S4" t="n">
-        <v>1033664000</v>
+        <v>1182042000</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.02</v>
+        <v>-0.14</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.02</v>
+        <v>-0.14</v>
       </c>
       <c r="V4" t="n">
-        <v>-1050184000</v>
+        <v>-170679000</v>
       </c>
       <c r="W4" t="n">
-        <v>-1050184000</v>
+        <v>-170679000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1050184000</v>
+        <v>-170679000</v>
       </c>
       <c r="Z4" t="n">
-        <v>10282000</v>
+        <v>-368000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1060466000</v>
+        <v>-170311000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1060466000</v>
+        <v>-170311000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-18679000</v>
+        <v>-15923000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1079145000</v>
+        <v>-186234000</v>
       </c>
       <c r="AE4" t="n">
-        <v>890000</v>
+        <v>1412000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-725744000</v>
+        <v>-23785000</v>
       </c>
       <c r="AG4" t="n">
-        <v>86000</v>
+        <v>10239000</v>
       </c>
       <c r="AH4" t="n">
-        <v>539452000</v>
+        <v>29000</v>
       </c>
       <c r="AI4" t="n">
-        <v>186206000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
+        <v>13517000</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>-80631000</v>
+        <v>-93937000</v>
       </c>
       <c r="AL4" t="n">
-        <v>80638000</v>
+        <v>93994000</v>
       </c>
       <c r="AM4" t="n">
-        <v>7000</v>
+        <v>57000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-134636000</v>
+        <v>-66147000</v>
       </c>
       <c r="AO4" t="n">
-        <v>197362000</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
+        <v>121523000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>11847000</v>
+      </c>
       <c r="AQ4" t="n">
-        <v>11678000</v>
+        <v>14907000</v>
       </c>
       <c r="AR4" t="n">
-        <v>195021000</v>
+        <v>95081000</v>
       </c>
       <c r="AS4" t="n">
-        <v>14954000</v>
+        <v>22050000</v>
       </c>
       <c r="AT4" t="n">
-        <v>180067000</v>
+        <v>73031000</v>
       </c>
       <c r="AU4" t="n">
-        <v>62726000</v>
+        <v>55376000</v>
       </c>
       <c r="AV4" t="n">
-        <v>390410000</v>
+        <v>308652000</v>
       </c>
       <c r="AW4" t="n">
-        <v>453136000</v>
+        <v>364028000</v>
       </c>
       <c r="AX4" t="n">
-        <v>453136000</v>
+        <v>364028000</v>
       </c>
     </row>
   </sheetData>
@@ -1493,7 +1493,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45382</v>
+        <v>44651</v>
       </c>
       <c r="B2" t="n">
         <v>1182042000</v>
@@ -1502,44 +1502,46 @@
         <v>1182042000</v>
       </c>
       <c r="D2" t="n">
-        <v>939690000</v>
+        <v>596598000</v>
       </c>
       <c r="E2" t="n">
-        <v>1055137000</v>
+        <v>743189000</v>
       </c>
       <c r="F2" t="n">
-        <v>-1040467000</v>
+        <v>52163000</v>
       </c>
       <c r="G2" t="n">
-        <v>-86667000</v>
+        <v>766909000</v>
       </c>
       <c r="H2" t="n">
-        <v>-1123635000</v>
+        <v>-242968000</v>
       </c>
       <c r="I2" t="n">
-        <v>-1040467000</v>
+        <v>52163000</v>
       </c>
       <c r="J2" t="n">
-        <v>103762000</v>
+        <v>125636000</v>
       </c>
       <c r="K2" t="n">
-        <v>-1038042000</v>
+        <v>149356000</v>
       </c>
       <c r="L2" t="n">
-        <v>-974412000</v>
+        <v>325894000</v>
       </c>
       <c r="M2" t="n">
-        <v>-1045345000</v>
+        <v>137509000</v>
       </c>
       <c r="N2" t="n">
-        <v>-7303000</v>
+        <v>-11847000</v>
       </c>
       <c r="O2" t="n">
-        <v>-1038042000</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>149356000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2562000</v>
+      </c>
       <c r="Q2" t="n">
-        <v>-1721511000</v>
+        <v>-526049000</v>
       </c>
       <c r="R2" t="n">
         <v>768937000</v>
@@ -1551,104 +1553,112 @@
         <v>118204000</v>
       </c>
       <c r="U2" t="n">
-        <v>1453279000</v>
+        <v>1043599000</v>
       </c>
       <c r="V2" t="n">
-        <v>212775000</v>
+        <v>343845000</v>
       </c>
       <c r="W2" t="n">
-        <v>14751000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
+        <v>13376000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>298000</v>
+      </c>
       <c r="Y2" t="n">
-        <v>28086000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
+        <v>33885000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
       <c r="AA2" t="n">
-        <v>146184000</v>
+        <v>266803000</v>
       </c>
       <c r="AB2" t="n">
-        <v>82554000</v>
+        <v>90265000</v>
       </c>
       <c r="AC2" t="n">
-        <v>63630000</v>
+        <v>176538000</v>
       </c>
       <c r="AD2" t="n">
-        <v>23754000</v>
+        <v>29483000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1240504000</v>
+        <v>699754000</v>
       </c>
       <c r="AF2" t="n">
-        <v>908953000</v>
+        <v>476386000</v>
       </c>
       <c r="AG2" t="n">
-        <v>21208000</v>
+        <v>35371000</v>
       </c>
       <c r="AH2" t="n">
-        <v>887745000</v>
+        <v>441015000</v>
       </c>
       <c r="AI2" t="n">
-        <v>311470000</v>
+        <v>206342000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>271912000</v>
+        <v>114370000</v>
       </c>
       <c r="AK2" t="n">
-        <v>33303000</v>
+        <v>76450000</v>
       </c>
       <c r="AL2" t="n">
-        <v>6255000</v>
+        <v>15522000</v>
       </c>
       <c r="AM2" t="n">
-        <v>407934000</v>
+        <v>1181108000</v>
       </c>
       <c r="AN2" t="n">
-        <v>291065000</v>
+        <v>724322000</v>
       </c>
       <c r="AO2" t="n">
-        <v>61504000</v>
+        <v>65835000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3542000</v>
+        <v>12825000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3542000</v>
+        <v>12825000</v>
       </c>
       <c r="AR2" t="n">
-        <v>5666000</v>
+        <v>191216000</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>87743000</v>
       </c>
       <c r="AT2" t="n">
-        <v>5666000</v>
+        <v>103473000</v>
       </c>
       <c r="AU2" t="n">
-        <v>2425000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+        <v>97193000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>94768000</v>
+      </c>
       <c r="AW2" t="n">
         <v>2425000</v>
       </c>
       <c r="AX2" t="n">
-        <v>217928000</v>
+        <v>357253000</v>
       </c>
       <c r="AY2" t="n">
-        <v>-448310000</v>
+        <v>-435301000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>666238000</v>
+        <v>792554000</v>
       </c>
       <c r="BA2" t="n">
-        <v>124769000</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
+        <v>133644000</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>284761000</v>
+      </c>
       <c r="BC2" t="n">
-        <v>40080000</v>
+        <v>93804000</v>
       </c>
       <c r="BD2" t="n">
-        <v>490905000</v>
+        <v>554622000</v>
       </c>
       <c r="BE2" t="n">
         <v>10484000</v>
@@ -1657,46 +1667,46 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>116869000</v>
+        <v>456786000</v>
       </c>
       <c r="BH2" t="n">
-        <v>781000</v>
+        <v>4443000</v>
       </c>
       <c r="BI2" t="n">
-        <v>54958000</v>
+        <v>251387000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>5521000</v>
+        <v>1500000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5521000</v>
+        <v>1500000</v>
       </c>
       <c r="BL2" t="n">
-        <v>957000</v>
+        <v>6449000</v>
       </c>
       <c r="BM2" t="n">
-        <v>625000</v>
+        <v>1159000</v>
       </c>
       <c r="BN2" t="n">
-        <v>41609000</v>
+        <v>170054000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-228130000</v>
+        <v>-98708000</v>
       </c>
       <c r="BP2" t="n">
-        <v>269739000</v>
+        <v>268762000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>12418000</v>
+        <v>21794000</v>
       </c>
       <c r="BR2" t="n">
-        <v>733000</v>
+        <v>839000</v>
       </c>
       <c r="BS2" t="n">
-        <v>11685000</v>
+        <v>20955000</v>
       </c>
       <c r="BT2" t="n">
-        <v>11685000</v>
+        <v>20955000</v>
       </c>
     </row>
     <row r="3">
@@ -1915,7 +1925,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44651</v>
+        <v>45382</v>
       </c>
       <c r="B4" t="n">
         <v>1182042000</v>
@@ -1924,46 +1934,44 @@
         <v>1182042000</v>
       </c>
       <c r="D4" t="n">
-        <v>596598000</v>
+        <v>939690000</v>
       </c>
       <c r="E4" t="n">
-        <v>743189000</v>
+        <v>1055137000</v>
       </c>
       <c r="F4" t="n">
-        <v>52163000</v>
+        <v>-1040467000</v>
       </c>
       <c r="G4" t="n">
-        <v>766909000</v>
+        <v>-86667000</v>
       </c>
       <c r="H4" t="n">
-        <v>-242968000</v>
+        <v>-1123635000</v>
       </c>
       <c r="I4" t="n">
-        <v>52163000</v>
+        <v>-1040467000</v>
       </c>
       <c r="J4" t="n">
-        <v>125636000</v>
+        <v>103762000</v>
       </c>
       <c r="K4" t="n">
-        <v>149356000</v>
+        <v>-1038042000</v>
       </c>
       <c r="L4" t="n">
-        <v>325894000</v>
+        <v>-974412000</v>
       </c>
       <c r="M4" t="n">
-        <v>137509000</v>
+        <v>-1045345000</v>
       </c>
       <c r="N4" t="n">
-        <v>-11847000</v>
+        <v>-7303000</v>
       </c>
       <c r="O4" t="n">
-        <v>149356000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2562000</v>
-      </c>
+        <v>-1038042000</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>-526049000</v>
+        <v>-1721511000</v>
       </c>
       <c r="R4" t="n">
         <v>768937000</v>
@@ -1975,112 +1983,104 @@
         <v>118204000</v>
       </c>
       <c r="U4" t="n">
-        <v>1043599000</v>
+        <v>1453279000</v>
       </c>
       <c r="V4" t="n">
-        <v>343845000</v>
+        <v>212775000</v>
       </c>
       <c r="W4" t="n">
-        <v>13376000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>298000</v>
-      </c>
+        <v>14751000</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>33885000</v>
-      </c>
-      <c r="Z4" t="n">
+        <v>28086000</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="n">
+        <v>146184000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>82554000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>63630000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>23754000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1240504000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>908953000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>21208000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>887745000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>311470000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>271912000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>33303000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>6255000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>407934000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>291065000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>61504000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>3542000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3542000</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5666000</v>
+      </c>
+      <c r="AS4" t="n">
         <v>0</v>
       </c>
-      <c r="AA4" t="n">
-        <v>266803000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>90265000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>176538000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>29483000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>699754000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>476386000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>35371000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>441015000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>206342000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>114370000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>76450000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>15522000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1181108000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>724322000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>65835000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>12825000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>12825000</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>191216000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>87743000</v>
-      </c>
       <c r="AT4" t="n">
-        <v>103473000</v>
+        <v>5666000</v>
       </c>
       <c r="AU4" t="n">
-        <v>97193000</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>94768000</v>
-      </c>
+        <v>2425000</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
         <v>2425000</v>
       </c>
       <c r="AX4" t="n">
-        <v>357253000</v>
+        <v>217928000</v>
       </c>
       <c r="AY4" t="n">
-        <v>-435301000</v>
+        <v>-448310000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>792554000</v>
+        <v>666238000</v>
       </c>
       <c r="BA4" t="n">
-        <v>133644000</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>284761000</v>
-      </c>
+        <v>124769000</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
-        <v>93804000</v>
+        <v>40080000</v>
       </c>
       <c r="BD4" t="n">
-        <v>554622000</v>
+        <v>490905000</v>
       </c>
       <c r="BE4" t="n">
         <v>10484000</v>
@@ -2089,46 +2089,46 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>456786000</v>
+        <v>116869000</v>
       </c>
       <c r="BH4" t="n">
-        <v>4443000</v>
+        <v>781000</v>
       </c>
       <c r="BI4" t="n">
-        <v>251387000</v>
+        <v>54958000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1500000</v>
+        <v>5521000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1500000</v>
+        <v>5521000</v>
       </c>
       <c r="BL4" t="n">
-        <v>6449000</v>
+        <v>957000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1159000</v>
+        <v>625000</v>
       </c>
       <c r="BN4" t="n">
-        <v>170054000</v>
+        <v>41609000</v>
       </c>
       <c r="BO4" t="n">
-        <v>-98708000</v>
+        <v>-228130000</v>
       </c>
       <c r="BP4" t="n">
-        <v>268762000</v>
+        <v>269739000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>21794000</v>
+        <v>12418000</v>
       </c>
       <c r="BR4" t="n">
-        <v>839000</v>
+        <v>733000</v>
       </c>
       <c r="BS4" t="n">
-        <v>20955000</v>
+        <v>11685000</v>
       </c>
       <c r="BT4" t="n">
-        <v>20955000</v>
+        <v>11685000</v>
       </c>
     </row>
   </sheetData>
@@ -2354,126 +2354,130 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45382</v>
+        <v>44651</v>
       </c>
       <c r="B2" t="n">
-        <v>87844000</v>
+        <v>-19371000</v>
       </c>
       <c r="C2" t="n">
-        <v>-30964000</v>
+        <v>-188689000</v>
       </c>
       <c r="D2" t="n">
-        <v>34953000</v>
+        <v>308452000</v>
       </c>
       <c r="E2" t="n">
-        <v>-1702000</v>
+        <v>-15854000</v>
       </c>
       <c r="F2" t="n">
-        <v>11685000</v>
+        <v>20955000</v>
       </c>
       <c r="G2" t="n">
-        <v>36242000</v>
+        <v>56012000</v>
       </c>
       <c r="H2" t="n">
-        <v>482000</v>
+        <v>-3864000</v>
       </c>
       <c r="I2" t="n">
-        <v>-25039000</v>
+        <v>-31193000</v>
       </c>
       <c r="J2" t="n">
-        <v>-118171000</v>
+        <v>38171000</v>
       </c>
       <c r="K2" t="n">
-        <v>-25000</v>
+        <v>-562000</v>
       </c>
       <c r="L2" t="n">
-        <v>-82238000</v>
+        <v>-35695000</v>
       </c>
       <c r="M2" t="n">
-        <v>3989000</v>
+        <v>119763000</v>
       </c>
       <c r="N2" t="n">
-        <v>3989000</v>
+        <v>119763000</v>
       </c>
       <c r="O2" t="n">
-        <v>-30964000</v>
+        <v>-188689000</v>
       </c>
       <c r="P2" t="n">
-        <v>34953000</v>
+        <v>308452000</v>
       </c>
       <c r="Q2" t="n">
-        <v>3586000</v>
+        <v>-65847000</v>
       </c>
       <c r="R2" t="n">
-        <v>4400000</v>
+        <v>-50000000</v>
       </c>
       <c r="S2" t="n">
-        <v>57000</v>
+        <v>7000</v>
       </c>
       <c r="T2" t="n">
-        <v>272000</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>272000</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-1143000</v>
+        <v>-15854000</v>
       </c>
       <c r="X2" t="n">
-        <v>559000</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1702000</v>
+        <v>-15854000</v>
       </c>
       <c r="Z2" t="n">
-        <v>89546000</v>
+        <v>-3517000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1005000</v>
+        <v>954000</v>
       </c>
       <c r="AB2" t="n">
-        <v>74276000</v>
+        <v>-48949000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-7002000</v>
+        <v>-77816000</v>
       </c>
       <c r="AD2" t="n">
-        <v>79366000</v>
+        <v>29302000</v>
       </c>
       <c r="AE2" t="n">
-        <v>863000</v>
+        <v>-639000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1049000</v>
+        <v>204000</v>
       </c>
       <c r="AG2" t="n">
-        <v>94063000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
+        <v>80783000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2562000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>537296000</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>66092000</v>
+        <v>172247000</v>
       </c>
       <c r="AK2" t="n">
-        <v>2188000</v>
+        <v>70286000</v>
       </c>
       <c r="AL2" t="n">
-        <v>63904000</v>
+        <v>101961000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1334000</v>
+        <v>1833000</v>
       </c>
       <c r="AN2" t="n">
-        <v>4149000</v>
+        <v>8794000</v>
       </c>
       <c r="AO2" t="n">
-        <v>11616000</v>
+        <v>465000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-186234000</v>
+        <v>-1079145000</v>
       </c>
     </row>
     <row r="3">
@@ -2604,130 +2608,126 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44651</v>
+        <v>45382</v>
       </c>
       <c r="B4" t="n">
-        <v>-19371000</v>
+        <v>87844000</v>
       </c>
       <c r="C4" t="n">
-        <v>-188689000</v>
+        <v>-30964000</v>
       </c>
       <c r="D4" t="n">
-        <v>308452000</v>
+        <v>34953000</v>
       </c>
       <c r="E4" t="n">
-        <v>-15854000</v>
+        <v>-1702000</v>
       </c>
       <c r="F4" t="n">
-        <v>20955000</v>
+        <v>11685000</v>
       </c>
       <c r="G4" t="n">
-        <v>56012000</v>
+        <v>36242000</v>
       </c>
       <c r="H4" t="n">
-        <v>-3864000</v>
+        <v>482000</v>
       </c>
       <c r="I4" t="n">
-        <v>-31193000</v>
+        <v>-25039000</v>
       </c>
       <c r="J4" t="n">
-        <v>38171000</v>
+        <v>-118171000</v>
       </c>
       <c r="K4" t="n">
-        <v>-562000</v>
+        <v>-25000</v>
       </c>
       <c r="L4" t="n">
-        <v>-35695000</v>
+        <v>-82238000</v>
       </c>
       <c r="M4" t="n">
-        <v>119763000</v>
+        <v>3989000</v>
       </c>
       <c r="N4" t="n">
-        <v>119763000</v>
+        <v>3989000</v>
       </c>
       <c r="O4" t="n">
-        <v>-188689000</v>
+        <v>-30964000</v>
       </c>
       <c r="P4" t="n">
-        <v>308452000</v>
+        <v>34953000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-65847000</v>
+        <v>3586000</v>
       </c>
       <c r="R4" t="n">
-        <v>-50000000</v>
+        <v>4400000</v>
       </c>
       <c r="S4" t="n">
-        <v>7000</v>
+        <v>57000</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>272000</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>272000</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-15854000</v>
+        <v>-1143000</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>559000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-15854000</v>
+        <v>-1702000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-3517000</v>
+        <v>89546000</v>
       </c>
       <c r="AA4" t="n">
-        <v>954000</v>
+        <v>-1005000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-48949000</v>
+        <v>74276000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-77816000</v>
+        <v>-7002000</v>
       </c>
       <c r="AD4" t="n">
-        <v>29302000</v>
+        <v>79366000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-639000</v>
+        <v>863000</v>
       </c>
       <c r="AF4" t="n">
-        <v>204000</v>
+        <v>1049000</v>
       </c>
       <c r="AG4" t="n">
-        <v>80783000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2562000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>537296000</v>
-      </c>
+        <v>94063000</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>172247000</v>
+        <v>66092000</v>
       </c>
       <c r="AK4" t="n">
-        <v>70286000</v>
+        <v>2188000</v>
       </c>
       <c r="AL4" t="n">
-        <v>101961000</v>
+        <v>63904000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1833000</v>
+        <v>1334000</v>
       </c>
       <c r="AN4" t="n">
-        <v>8794000</v>
+        <v>4149000</v>
       </c>
       <c r="AO4" t="n">
-        <v>465000</v>
+        <v>11616000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1079145000</v>
+        <v>-186234000</v>
       </c>
     </row>
   </sheetData>
@@ -3237,192 +3237,192 @@
       </c>
       <c r="CU1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
         <is>
           <t>longName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EG1" t="inlineStr">
@@ -3555,7 +3555,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.658</v>
+        <v>0.634</v>
       </c>
       <c r="AF2" t="n">
         <v>1796000</v>
@@ -3585,16 +3585,16 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>60284140</v>
+        <v>6028414</v>
       </c>
       <c r="AP2" t="n">
-        <v>60284142</v>
+        <v>6028414</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.05</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.052</v>
+        <v>0.51</v>
       </c>
       <c r="AS2" t="n">
         <v>6.25</v>
@@ -3603,13 +3603,13 @@
         <v>0.02</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.17768046</v>
+        <v>0.017768048</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.051</v>
+        <v>0.11526</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.051</v>
+        <v>0.067065</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1109360128</v>
+        <v>1055104384</v>
       </c>
       <c r="BC2" t="n">
         <v>-0.28708</v>
       </c>
       <c r="BD2" t="n">
-        <v>1182042000</v>
+        <v>118204200</v>
       </c>
       <c r="BE2" t="n">
         <v>0.13813</v>
@@ -3641,10 +3641,10 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>1182042000</v>
+        <v>118204200</v>
       </c>
       <c r="BH2" t="n">
-        <v>-0.964</v>
+        <v>-9.635</v>
       </c>
       <c r="BI2" t="n">
         <v>1743379200</v>
@@ -3659,7 +3659,7 @@
         <v>-97401000</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.73</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
@@ -3670,19 +3670,19 @@
         <v>1780876800</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.27</v>
+        <v>3.11</v>
       </c>
       <c r="BQ2" t="n">
-        <v>46.997</v>
+        <v>44.698</v>
       </c>
       <c r="BR2" t="n">
         <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.023</v>
+        <v>0.23</v>
       </c>
       <c r="BU2" t="n">
         <v>1567123200</v>
@@ -3704,7 +3704,7 @@
         <v>12964000</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.011</v>
+        <v>0.11</v>
       </c>
       <c r="CA2" t="n">
         <v>23605000</v>
@@ -3722,7 +3722,7 @@
         <v>339284000</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.287</v>
+        <v>2.87</v>
       </c>
       <c r="CG2" t="n">
         <v>-0.012560001</v>
@@ -3782,141 +3782,141 @@
       </c>
       <c r="CU2" t="inlineStr">
         <is>
+          <t>CA CULTURAL</t>
+        </is>
+      </c>
+      <c r="CV2" t="n">
+        <v>1.9999967</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
           <t>PRE</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CY2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>finmb_280427680</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="DA2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="DB2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="CZ2" t="n">
+      <c r="DC2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DD2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DB2" t="b">
+      <c r="DE2" t="b">
         <v>0</v>
       </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>CA CULTURAL</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0.0009999983000000001</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0.019999966</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>0.05 - 0.51</t>
+        </is>
+      </c>
+      <c r="DK2" t="n">
+        <v>-0.459</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>1732881628</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1732881628</v>
+      </c>
+      <c r="DP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.06426</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.5575221</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.016065001</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.23954375</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.0052932017</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1731656683</v>
+      </c>
+      <c r="EA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1426123800000</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.0009999983000000001</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>0.05 - 0.052</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
         <is>
           <t>CA Cultural Technology Group Limited</t>
         </is>
-      </c>
-      <c r="DE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>0.0009999983000000001</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>0.019999966</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>0.05 - 0.052</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>-0.001000002</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>-0.019230807</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>1732881628</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>1732881628</v>
-      </c>
-      <c r="DN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.052904565</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>1426123800000</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0.0009999983000000001</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>0.05 - 0.052</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="ED2" t="n">
-        <v>1731656683</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>1.9999967</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>0.051</v>
       </c>
       <c r="EG2" t="inlineStr"/>
     </row>
